--- a/content/images/BrAPI_Application_Chart.xlsx
+++ b/content/images/BrAPI_Application_Chart.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ps664\Documents\Letters_Reports_Publications\BrAPI-Manuscript2\content\images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.4\home\rafael\git\BrAPI-Manuscript2\content\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A88C2D-71E3-4529-9C5E-C6B592DFE007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1136AD89-7CE2-4D2D-9576-C479C57803D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{8D6FC713-DE86-495E-930B-D50DF992A6EC}"/>
+    <workbookView xWindow="2124" yWindow="2472" windowWidth="24636" windowHeight="13500" xr2:uid="{8D6FC713-DE86-495E-930B-D50DF992A6EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$S$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A:$T</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="38">
   <si>
     <t>Core</t>
   </si>
@@ -889,20 +889,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB48"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="0.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="43" style="31" customWidth="1"/>
-    <col min="3" max="6" width="8.42578125" style="32" customWidth="1"/>
-    <col min="7" max="10" width="8.42578125" style="33" customWidth="1"/>
-    <col min="11" max="14" width="8.42578125" style="34" customWidth="1"/>
-    <col min="15" max="18" width="8.42578125" style="35" customWidth="1"/>
-    <col min="19" max="19" width="0.85546875" style="1" customWidth="1"/>
-    <col min="20" max="28" width="9.140625" style="1"/>
-    <col min="29" max="16384" width="9.140625" style="3"/>
+    <col min="3" max="6" width="8.44140625" style="32" customWidth="1"/>
+    <col min="7" max="10" width="8.44140625" style="33" customWidth="1"/>
+    <col min="11" max="14" width="8.44140625" style="34" customWidth="1"/>
+    <col min="15" max="18" width="8.44140625" style="35" customWidth="1"/>
+    <col min="19" max="19" width="0.88671875" style="1" customWidth="1"/>
+    <col min="20" max="28" width="9.109375" style="1"/>
+    <col min="29" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -921,7 +921,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="2:18" ht="21" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="21.6" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="36" t="s">
         <v>0</v>
@@ -948,7 +948,7 @@
       <c r="Q2" s="40"/>
       <c r="R2" s="41"/>
     </row>
-    <row r="3" spans="2:18" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
         <v>7</v>
@@ -999,7 +999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1024,7 +1024,7 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="18"/>
     </row>
-    <row r="5" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
         <v>9</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="Q5" s="23"/>
       <c r="R5" s="24"/>
     </row>
-    <row r="6" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>10</v>
       </c>
@@ -1080,7 +1080,7 @@
       <c r="Q6" s="23"/>
       <c r="R6" s="24"/>
     </row>
-    <row r="7" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
         <v>11</v>
       </c>
@@ -1107,7 +1107,7 @@
       <c r="Q7" s="23"/>
       <c r="R7" s="24"/>
     </row>
-    <row r="8" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>12</v>
       </c>
@@ -1138,7 +1138,7 @@
       <c r="Q8" s="23"/>
       <c r="R8" s="24"/>
     </row>
-    <row r="9" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>13</v>
       </c>
@@ -1154,8 +1154,12 @@
       <c r="H9" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="I9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="K9" s="22"/>
       <c r="L9" s="22"/>
       <c r="M9" s="22"/>
@@ -1167,7 +1171,7 @@
       <c r="Q9" s="23"/>
       <c r="R9" s="24"/>
     </row>
-    <row r="10" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
         <v>14</v>
       </c>
@@ -1190,7 +1194,7 @@
       <c r="Q10" s="29"/>
       <c r="R10" s="30"/>
     </row>
-    <row r="11" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>20</v>
       </c>
@@ -1213,7 +1217,7 @@
       <c r="Q11" s="17"/>
       <c r="R11" s="18"/>
     </row>
-    <row r="12" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>16</v>
       </c>
@@ -1238,7 +1242,7 @@
       <c r="Q12" s="23"/>
       <c r="R12" s="24"/>
     </row>
-    <row r="13" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
@@ -1265,7 +1269,7 @@
       <c r="Q13" s="23"/>
       <c r="R13" s="24"/>
     </row>
-    <row r="14" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>15</v>
       </c>
@@ -1292,7 +1296,7 @@
       <c r="Q14" s="23"/>
       <c r="R14" s="24"/>
     </row>
-    <row r="15" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
         <v>18</v>
       </c>
@@ -1319,7 +1323,7 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="24"/>
     </row>
-    <row r="16" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>19</v>
       </c>
@@ -1346,7 +1350,7 @@
       <c r="Q16" s="29"/>
       <c r="R16" s="30"/>
     </row>
-    <row r="17" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>37</v>
       </c>
@@ -1379,7 +1383,7 @@
       <c r="Q17" s="17"/>
       <c r="R17" s="18"/>
     </row>
-    <row r="18" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
         <v>24</v>
       </c>
@@ -1404,7 +1408,7 @@
       </c>
       <c r="R18" s="24"/>
     </row>
-    <row r="19" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="s">
         <v>23</v>
       </c>
@@ -1429,7 +1433,7 @@
       <c r="Q19" s="23"/>
       <c r="R19" s="24"/>
     </row>
-    <row r="20" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="19" t="s">
         <v>22</v>
       </c>
@@ -1458,7 +1462,7 @@
       </c>
       <c r="R20" s="24"/>
     </row>
-    <row r="21" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="25" t="s">
         <v>21</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
@@ -1528,7 +1532,7 @@
       </c>
       <c r="R22" s="18"/>
     </row>
-    <row r="23" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
         <v>27</v>
       </c>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="R23" s="24"/>
     </row>
-    <row r="24" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
         <v>28</v>
       </c>
@@ -1610,7 +1614,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
         <v>26</v>
       </c>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="R25" s="24"/>
     </row>
-    <row r="26" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>25</v>
       </c>
@@ -1680,7 +1684,7 @@
       </c>
       <c r="R26" s="24"/>
     </row>
-    <row r="27" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="25" t="s">
         <v>30</v>
       </c>
@@ -1717,7 +1721,7 @@
       </c>
       <c r="R27" s="30"/>
     </row>
-    <row r="28" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" ht="39.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>33</v>
       </c>
@@ -1746,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>31</v>
       </c>
@@ -1775,7 +1779,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
         <v>32</v>
       </c>
@@ -1812,7 +1816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>34</v>
       </c>
@@ -1837,7 +1841,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="25" t="s">
         <v>36</v>
       </c>
@@ -1874,52 +1878,52 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:2" s="1" customFormat="1" ht="21" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" s="1" customFormat="1" ht="21.6" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="2"/>
     </row>
   </sheetData>
@@ -1931,6 +1935,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="8" scale="90" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="84" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>